--- a/artfynd/A 40386-2025 artfynd.xlsx
+++ b/artfynd/A 40386-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128864380</v>
       </c>
       <c r="B2" t="n">
-        <v>57831</v>
+        <v>57834</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>128864350</v>
       </c>
       <c r="B3" t="n">
-        <v>56917</v>
+        <v>56920</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>128864260</v>
       </c>
       <c r="B4" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 40386-2025 artfynd.xlsx
+++ b/artfynd/A 40386-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128864380</v>
       </c>
       <c r="B2" t="n">
-        <v>57834</v>
+        <v>57839</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>128864350</v>
       </c>
       <c r="B3" t="n">
-        <v>56920</v>
+        <v>56925</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>128864260</v>
       </c>
       <c r="B4" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 40386-2025 artfynd.xlsx
+++ b/artfynd/A 40386-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128864380</v>
       </c>
       <c r="B2" t="n">
-        <v>57839</v>
+        <v>57840</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>128864350</v>
       </c>
       <c r="B3" t="n">
-        <v>56925</v>
+        <v>56926</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>128864260</v>
       </c>
       <c r="B4" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 40386-2025 artfynd.xlsx
+++ b/artfynd/A 40386-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,60 +675,51 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128864380</v>
+        <v>128769492</v>
       </c>
       <c r="B2" t="n">
-        <v>57840</v>
+        <v>78742</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103031</v>
+        <v>502</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Ladlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Calicium tigillare</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Pers.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Nära Gråberget, Jmt</t>
+          <t>Nedom Gråberget, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>447089</v>
+        <v>447072</v>
       </c>
       <c r="R2" t="n">
-        <v>6992248</v>
+        <v>6992045</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,17 +746,28 @@
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -784,64 +786,51 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128864350</v>
+        <v>128864289</v>
       </c>
       <c r="B3" t="n">
-        <v>56926</v>
+        <v>78742</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>502</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ladlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Calicium tigillare</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Pers.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>nedom Gråberget , Jmt</t>
+          <t>Torraka på myr, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>447036</v>
+        <v>447106</v>
       </c>
       <c r="R3" t="n">
-        <v>6992278</v>
+        <v>6991997</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,6 +868,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -897,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128864260</v>
+        <v>128864305</v>
       </c>
       <c r="B4" t="n">
-        <v>57736</v>
+        <v>78334</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -908,38 +898,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6487</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>På tall, Jmt</t>
+          <t>Torraka på myr, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>447003</v>
+        <v>447106</v>
       </c>
       <c r="R4" t="n">
-        <v>6992402</v>
+        <v>6991997</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -974,17 +963,13 @@
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1000,6 +985,440 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128864260</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>På tall, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>447003</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6992402</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Marby</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Mona Olsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Mona Olsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128864350</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>nedom Gråberget , Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>447036</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6992278</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Marby</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Mona Olsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Mona Olsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128864380</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Nära Gråberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>447089</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6992248</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Marby</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Mona Olsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Mona Olsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128864231</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>I norra myrkanten, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>446985</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6992394</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Marby</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Mona Olsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Mona Olsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 40386-2025 artfynd.xlsx
+++ b/artfynd/A 40386-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128769492</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128864289</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -985,6 +1000,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128864305</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1091,6 +1111,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128864260</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1204,6 +1229,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128864350</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1313,6 +1343,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128864380</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1419,8 +1454,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128864231</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>